--- a/ResourcesBD/basepack.xlsx
+++ b/ResourcesBD/basepack.xlsx
@@ -464,6 +464,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
